--- a/academias/Ciencias Sociales - Estadisticos 20212.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20212.xlsx
@@ -486,22 +486,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -518,22 +521,25 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -550,22 +556,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -582,22 +591,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -846,22 +858,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -878,22 +893,25 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -910,22 +928,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -942,22 +963,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I5" s="2">
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20212.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20212.xlsx
@@ -678,22 +678,25 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.5</v>
       </c>
       <c r="J2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -710,22 +713,25 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.5</v>
       </c>
       <c r="J3">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -742,22 +748,25 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I4" s="2">
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -774,22 +783,25 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>21.21</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -870,7 +882,7 @@
         <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -905,7 +917,7 @@
         <v>4.55</v>
       </c>
       <c r="I3" s="2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -928,19 +940,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>30.3</v>
+        <v>18.18</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -963,19 +975,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>69.7</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5" s="1">
-        <v>30.3</v>
+        <v>21.21</v>
       </c>
       <c r="I5" s="2">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20212.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20212.xlsx
@@ -870,19 +870,19 @@
         <v>22</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -905,19 +905,19 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -940,19 +940,19 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>81.81999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H4" s="1">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="I4" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -975,19 +975,19 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>78.79000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="H5" s="1">
-        <v>21.21</v>
+        <v>9.09</v>
       </c>
       <c r="I5" s="2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>0</v>
